--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:42</t>
+    <t xml:space="preserve">2026-09-09 23:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:42</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:31</t>
+    <t xml:space="preserve">2026-09-23 13:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 13:03</t>
+    <t xml:space="preserve">2026-10-02 15:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Quirihue</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Coihueco</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:19</t>
+    <t xml:space="preserve">2026-10-04 09:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_p_basica_a_2020_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:48</t>
+    <t xml:space="preserve">2026-10-05 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
